--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ90"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6387,10 +6387,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120721948</v>
+        <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>92841</v>
+        <v>93423</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6398,21 +6398,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6422,13 +6422,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550526</v>
+        <v>550502</v>
       </c>
       <c r="R57" t="n">
-        <v>6964481</v>
+        <v>6964602</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6452,12 +6452,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6472,27 +6482,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120721948</t>
+          <t>https://artportalen.se/Sighting/136858640</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120721949</v>
+        <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>92841</v>
+        <v>93423</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6500,37 +6510,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550505</v>
+        <v>550496</v>
       </c>
       <c r="R58" t="n">
-        <v>6964580</v>
+        <v>6964594</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6554,12 +6568,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6574,24 +6598,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120721949</t>
+          <t>https://artportalen.se/Sighting/136858641</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120721951</v>
+        <v>120721948</v>
       </c>
       <c r="B59" t="n">
         <v>92841</v>
@@ -6626,10 +6650,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550615</v>
+        <v>550526</v>
       </c>
       <c r="R59" t="n">
-        <v>6964651</v>
+        <v>6964481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6687,51 +6711,51 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120721951</t>
+          <t>https://artportalen.se/Sighting/120721948</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113232489</v>
+        <v>120721949</v>
       </c>
       <c r="B60" t="n">
-        <v>91872</v>
+        <v>92841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>4745</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550811</v>
+        <v>550505</v>
       </c>
       <c r="R60" t="n">
-        <v>6964810</v>
+        <v>6964580</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6758,12 +6782,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6778,66 +6802,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113232489</t>
+          <t>https://artportalen.se/Sighting/120721949</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113232811</v>
+        <v>120721951</v>
       </c>
       <c r="B61" t="n">
-        <v>90691</v>
+        <v>92841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550652</v>
+        <v>550615</v>
       </c>
       <c r="R61" t="n">
-        <v>6964521</v>
+        <v>6964651</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6864,12 +6884,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6884,66 +6904,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113232811</t>
+          <t>https://artportalen.se/Sighting/120721951</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120722010</v>
+        <v>113232489</v>
       </c>
       <c r="B62" t="n">
-        <v>90691</v>
+        <v>91872</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6276</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550507</v>
+        <v>550811</v>
       </c>
       <c r="R62" t="n">
-        <v>6964571</v>
+        <v>6964810</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6970,12 +6986,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6990,24 +7006,28 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120722010</t>
+          <t>https://artportalen.se/Sighting/113232489</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120722011</v>
+        <v>113232811</v>
       </c>
       <c r="B63" t="n">
         <v>90691</v>
@@ -7038,14 +7058,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550470</v>
+        <v>550652</v>
       </c>
       <c r="R63" t="n">
-        <v>6964613</v>
+        <v>6964521</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,12 +7092,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7092,27 +7112,31 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120722011</t>
+          <t>https://artportalen.se/Sighting/113232811</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120721943</v>
+        <v>120722010</v>
       </c>
       <c r="B64" t="n">
-        <v>90710</v>
+        <v>90691</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7120,21 +7144,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7144,10 +7168,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550585</v>
+        <v>550507</v>
       </c>
       <c r="R64" t="n">
-        <v>6964561</v>
+        <v>6964571</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7205,16 +7229,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120721943</t>
+          <t>https://artportalen.se/Sighting/120722010</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>109838400</v>
+        <v>120722011</v>
       </c>
       <c r="B65" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7222,34 +7246,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550537</v>
+        <v>550470</v>
       </c>
       <c r="R65" t="n">
-        <v>6964445</v>
+        <v>6964613</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7276,12 +7300,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7296,62 +7320,62 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838400</t>
+          <t>https://artportalen.se/Sighting/120722011</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>109838392</v>
+        <v>120721943</v>
       </c>
       <c r="B66" t="n">
-        <v>78730</v>
+        <v>90710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>6286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550450</v>
+        <v>550585</v>
       </c>
       <c r="R66" t="n">
-        <v>6964486</v>
+        <v>6964561</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7378,12 +7402,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7398,49 +7422,49 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838392</t>
+          <t>https://artportalen.se/Sighting/120721943</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>109838402</v>
+        <v>109838400</v>
       </c>
       <c r="B67" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7450,10 +7474,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550538</v>
+        <v>550537</v>
       </c>
       <c r="R67" t="n">
-        <v>6964435</v>
+        <v>6964445</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7511,16 +7535,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838402</t>
+          <t>https://artportalen.se/Sighting/109838400</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>109838386</v>
+        <v>109838392</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7528,21 +7552,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7552,10 +7576,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550455</v>
+        <v>550450</v>
       </c>
       <c r="R68" t="n">
-        <v>6964571</v>
+        <v>6964486</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7613,16 +7637,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838386</t>
+          <t>https://artportalen.se/Sighting/109838392</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>109729411</v>
+        <v>109838402</v>
       </c>
       <c r="B69" t="n">
-        <v>79946</v>
+        <v>83307</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7630,21 +7654,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7654,10 +7678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550642</v>
+        <v>550538</v>
       </c>
       <c r="R69" t="n">
-        <v>6964548</v>
+        <v>6964435</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7684,12 +7708,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7704,27 +7728,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109729411</t>
+          <t>https://artportalen.se/Sighting/109838402</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>109729420</v>
+        <v>109838386</v>
       </c>
       <c r="B70" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7732,21 +7756,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7756,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550640</v>
+        <v>550455</v>
       </c>
       <c r="R70" t="n">
-        <v>6964470</v>
+        <v>6964571</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7786,12 +7810,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7806,24 +7830,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109729420</t>
+          <t>https://artportalen.se/Sighting/109838386</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>109838381</v>
+        <v>109729411</v>
       </c>
       <c r="B71" t="n">
         <v>79946</v>
@@ -7858,10 +7882,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550562</v>
+        <v>550642</v>
       </c>
       <c r="R71" t="n">
-        <v>6964484</v>
+        <v>6964548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7888,12 +7912,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7908,24 +7932,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838381</t>
+          <t>https://artportalen.se/Sighting/109729411</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>109838382</v>
+        <v>109729420</v>
       </c>
       <c r="B72" t="n">
         <v>79946</v>
@@ -7960,10 +7984,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550536</v>
+        <v>550640</v>
       </c>
       <c r="R72" t="n">
-        <v>6964589</v>
+        <v>6964470</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7990,12 +8014,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8010,24 +8034,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838382</t>
+          <t>https://artportalen.se/Sighting/109729420</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>109838384</v>
+        <v>109838381</v>
       </c>
       <c r="B73" t="n">
         <v>79946</v>
@@ -8062,10 +8086,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550455</v>
+        <v>550562</v>
       </c>
       <c r="R73" t="n">
-        <v>6964571</v>
+        <v>6964484</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8123,13 +8147,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838384</t>
+          <t>https://artportalen.se/Sighting/109838381</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>109838388</v>
+        <v>109838382</v>
       </c>
       <c r="B74" t="n">
         <v>79946</v>
@@ -8164,10 +8188,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550495</v>
+        <v>550536</v>
       </c>
       <c r="R74" t="n">
-        <v>6964512</v>
+        <v>6964589</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8225,13 +8249,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838388</t>
+          <t>https://artportalen.se/Sighting/109838382</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>109838395</v>
+        <v>109838384</v>
       </c>
       <c r="B75" t="n">
         <v>79946</v>
@@ -8266,10 +8290,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550479</v>
+        <v>550455</v>
       </c>
       <c r="R75" t="n">
-        <v>6964446</v>
+        <v>6964571</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8327,13 +8351,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838395</t>
+          <t>https://artportalen.se/Sighting/109838384</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>109838399</v>
+        <v>109838388</v>
       </c>
       <c r="B76" t="n">
         <v>79946</v>
@@ -8368,10 +8392,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550504</v>
+        <v>550495</v>
       </c>
       <c r="R76" t="n">
-        <v>6964453</v>
+        <v>6964512</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8429,16 +8453,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838399</t>
+          <t>https://artportalen.se/Sighting/109838388</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>109729422</v>
+        <v>109838395</v>
       </c>
       <c r="B77" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8446,21 +8470,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8470,10 +8494,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550640</v>
+        <v>550479</v>
       </c>
       <c r="R77" t="n">
-        <v>6964470</v>
+        <v>6964446</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8500,12 +8524,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8520,27 +8544,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109729422</t>
+          <t>https://artportalen.se/Sighting/109838395</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>109838380</v>
+        <v>109838399</v>
       </c>
       <c r="B78" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8548,21 +8572,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8572,10 +8596,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550562</v>
+        <v>550504</v>
       </c>
       <c r="R78" t="n">
-        <v>6964484</v>
+        <v>6964453</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8633,13 +8657,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838380</t>
+          <t>https://artportalen.se/Sighting/109838399</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>109838383</v>
+        <v>109729422</v>
       </c>
       <c r="B79" t="n">
         <v>79085</v>
@@ -8674,10 +8698,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550536</v>
+        <v>550640</v>
       </c>
       <c r="R79" t="n">
-        <v>6964589</v>
+        <v>6964470</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8704,12 +8728,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8724,24 +8748,24 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838383</t>
+          <t>https://artportalen.se/Sighting/109729422</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>109838385</v>
+        <v>109838380</v>
       </c>
       <c r="B80" t="n">
         <v>79085</v>
@@ -8776,10 +8800,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550455</v>
+        <v>550562</v>
       </c>
       <c r="R80" t="n">
-        <v>6964571</v>
+        <v>6964484</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,13 +8861,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838385</t>
+          <t>https://artportalen.se/Sighting/109838380</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>109838389</v>
+        <v>109838383</v>
       </c>
       <c r="B81" t="n">
         <v>79085</v>
@@ -8878,10 +8902,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550495</v>
+        <v>550536</v>
       </c>
       <c r="R81" t="n">
-        <v>6964512</v>
+        <v>6964589</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8939,13 +8963,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838389</t>
+          <t>https://artportalen.se/Sighting/109838383</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>109838393</v>
+        <v>109838385</v>
       </c>
       <c r="B82" t="n">
         <v>79085</v>
@@ -8980,10 +9004,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550450</v>
+        <v>550455</v>
       </c>
       <c r="R82" t="n">
-        <v>6964486</v>
+        <v>6964571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9041,13 +9065,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838393</t>
+          <t>https://artportalen.se/Sighting/109838385</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>109838394</v>
+        <v>109838389</v>
       </c>
       <c r="B83" t="n">
         <v>79085</v>
@@ -9082,10 +9106,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550479</v>
+        <v>550495</v>
       </c>
       <c r="R83" t="n">
-        <v>6964446</v>
+        <v>6964512</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9143,13 +9167,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838394</t>
+          <t>https://artportalen.se/Sighting/109838389</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>109838397</v>
+        <v>109838393</v>
       </c>
       <c r="B84" t="n">
         <v>79085</v>
@@ -9184,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550504</v>
+        <v>550450</v>
       </c>
       <c r="R84" t="n">
-        <v>6964453</v>
+        <v>6964486</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9245,13 +9269,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838397</t>
+          <t>https://artportalen.se/Sighting/109838393</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>109838470</v>
+        <v>109838394</v>
       </c>
       <c r="B85" t="n">
         <v>79085</v>
@@ -9286,10 +9310,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550538</v>
+        <v>550479</v>
       </c>
       <c r="R85" t="n">
-        <v>6964600</v>
+        <v>6964446</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9316,12 +9340,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9347,16 +9371,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838470</t>
+          <t>https://artportalen.se/Sighting/109838394</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>109729421</v>
+        <v>109838397</v>
       </c>
       <c r="B86" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9364,21 +9388,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9412,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550640</v>
+        <v>550504</v>
       </c>
       <c r="R86" t="n">
-        <v>6964470</v>
+        <v>6964453</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9418,12 +9442,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9438,27 +9462,27 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109729421</t>
+          <t>https://artportalen.se/Sighting/109838397</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>109838391</v>
+        <v>109838470</v>
       </c>
       <c r="B87" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9466,21 +9490,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9490,10 +9514,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550450</v>
+        <v>550538</v>
       </c>
       <c r="R87" t="n">
-        <v>6964486</v>
+        <v>6964600</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9520,12 +9544,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9551,13 +9575,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838391</t>
+          <t>https://artportalen.se/Sighting/109838470</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>109838398</v>
+        <v>109729421</v>
       </c>
       <c r="B88" t="n">
         <v>79917</v>
@@ -9592,10 +9616,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550504</v>
+        <v>550640</v>
       </c>
       <c r="R88" t="n">
-        <v>6964453</v>
+        <v>6964470</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9622,12 +9646,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9642,27 +9666,27 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109838398</t>
+          <t>https://artportalen.se/Sighting/109729421</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113232832</v>
+        <v>109838391</v>
       </c>
       <c r="B89" t="n">
-        <v>91402</v>
+        <v>79917</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9670,34 +9694,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>256703</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550412</v>
+        <v>550450</v>
       </c>
       <c r="R89" t="n">
-        <v>6964365</v>
+        <v>6964486</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9724,12 +9748,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9744,31 +9768,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113232832</t>
+          <t>https://artportalen.se/Sighting/109838391</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120722012</v>
+        <v>109838398</v>
       </c>
       <c r="B90" t="n">
-        <v>91431</v>
+        <v>79917</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9776,34 +9796,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6039941</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550640</v>
+        <v>550504</v>
       </c>
       <c r="R90" t="n">
-        <v>6964488</v>
+        <v>6964453</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9830,12 +9850,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9850,16 +9870,224 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838398</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>113232832</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>550412</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6964365</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232832</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120722012</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>550640</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6964488</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120722012</t>
         </is>
@@ -9956,6 +10184,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -6390,7 +6390,7 @@
         <v>136858640</v>
       </c>
       <c r="B57" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>136858641</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
